--- a/deepseek/huoxing_balance.xlsx
+++ b/deepseek/huoxing_balance.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,6 +485,1462 @@
       </c>
       <c r="C3" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-23 15:40</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-23 15:50</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:00</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:10</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:20</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:30</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:40</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:50</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-23 17:00</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-23 17:10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-23 17:20</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-23 17:30</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-23 17:40</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-23 17:50</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:00</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:10</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:20</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:30</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:40</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:50</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-23 19:00</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-23 19:10</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-23 19:20</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-23 19:30</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-23 19:40</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-23 19:50</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-23 20:00</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-23 20:10</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-23 20:20</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-23 20:30</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-23 20:40</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-23 20:50</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:00</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:10</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:20</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:30</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:40</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:50</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-23 22:00</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-23 22:10</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-23 22:20</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-23 22:30</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-23 22:40</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-23 22:50</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-23 23:00</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-23 23:10</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-23 23:20</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-23 23:30</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-23 23:40</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-23 23:50</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-24 00:00</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-24 00:10</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-24 00:20</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-24 00:30</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-24 00:40</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-24 00:50</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-24 01:00</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-24 01:10</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-24 01:20</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-24 01:30</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-24 01:40</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-24 01:50</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-24 02:10</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-24 02:20</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-24 02:30</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-24 02:40</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-24 02:50</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:00</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:10</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:20</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:30</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:40</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:50</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-24 04:00</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-24 04:10</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-24 04:20</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-24 04:30</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-24 04:40</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-24 04:50</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-24 05:00</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-24 05:10</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-24 05:20</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-24 05:30</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-24 05:40</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-24 05:50</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-24 06:00</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-24 06:10</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-24 06:20</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-24 06:30</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-24 06:40</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-24 06:50</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-24 07:00</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-24 07:10</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-24 07:20</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-24 07:30</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-24 07:40</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-24 07:50</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-24 08:00</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-24 08:10</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-24 08:20</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-24 08:30</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-24 08:40</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-24 08:50</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:00</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:10</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:20</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:30</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:40</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:50</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-24 10:00</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-24 10:10</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-24 10:20</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>10</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -498,7 +1954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -554,12 +2010,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$10.71</t>
+          <t>$10.20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$0.51</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -568,6 +2024,38 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$10.20</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>$10.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>$0.20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
